--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484640_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484640_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6415</v>
+        <v>8.520799999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4632</v>
+        <v>5.3426</v>
       </c>
       <c r="F2" t="n">
         <v>3.1782</v>
@@ -610,10 +610,10 @@
         <v>2.5656</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6953</v>
+        <v>0.184</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6795</v>
+        <v>0.1999</v>
       </c>
       <c r="U2" t="n">
         <v>-0.0159</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6685</v>
+        <v>6.0563</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6631</v>
+        <v>5.8528</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0053</v>
+        <v>0.2035</v>
       </c>
       <c r="G3" t="n">
         <v>2.3909</v>
@@ -688,13 +688,13 @@
         <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6336</v>
+        <v>1.0215</v>
       </c>
       <c r="T3" t="n">
-        <v>1.629</v>
+        <v>0.8186</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0047</v>
+        <v>0.2029</v>
       </c>
       <c r="V3" t="n">
         <v>1.9109</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.3453</v>
+        <v>5.5125</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0417</v>
+        <v>6.4814</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6964</v>
+        <v>-0.9689</v>
       </c>
       <c r="G4" t="n">
         <v>6.5096</v>
@@ -766,13 +766,13 @@
         <v>1.4661</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1251</v>
+        <v>0.042</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2753</v>
+        <v>0.1644</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1501</v>
+        <v>-0.1224</v>
       </c>
       <c r="V4" t="n">
         <v>-1.5889</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7363</v>
+        <v>2.9423</v>
       </c>
       <c r="E5" t="n">
-        <v>6.3506</v>
+        <v>5.5814</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.6143</v>
+        <v>-2.6391</v>
       </c>
       <c r="G5" t="n">
         <v>6.2157</v>
@@ -844,13 +844,13 @@
         <v>0.733</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8817</v>
+        <v>0.0877</v>
       </c>
       <c r="T5" t="n">
-        <v>1.08</v>
+        <v>0.3107</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1983</v>
+        <v>-0.2231</v>
       </c>
       <c r="V5" t="n">
         <v>-3.1778</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X. CORTINA CAMPOS</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8197</v>
+        <v>2.8748</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6771</v>
+        <v>1.1754</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1427</v>
+        <v>1.6994</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2881</v>
+        <v>5.0381</v>
       </c>
       <c r="H6" t="n">
-        <v>0.522</v>
+        <v>-0.1808</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7661</v>
+        <v>5.2188</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5677</v>
+        <v>4.585</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4427</v>
+        <v>-0.0249</v>
       </c>
       <c r="L6" t="n">
-        <v>0.125</v>
+        <v>4.6099</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7204</v>
+        <v>0.4531</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0793</v>
+        <v>-0.1558</v>
       </c>
       <c r="O6" t="n">
-        <v>0.641</v>
+        <v>0.6089</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9163</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9163</v>
+        <v>1.2828</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0181</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4759</v>
+        <v>-0.0377</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.494</v>
+        <v>-0.026</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6335</v>
+        <v>-0.6335</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6335</v>
+        <v>-0.6231</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5637</v>
+        <v>2.8085</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5975</v>
+        <v>1.6936</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9661999999999999</v>
+        <v>1.1148</v>
       </c>
       <c r="G7" t="n">
         <v>1.4932</v>
@@ -1000,13 +1000,13 @@
         <v>1.6493</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0259</v>
+        <v>0.2707</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4389</v>
+        <v>0.5351</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.413</v>
+        <v>-0.2643</v>
       </c>
       <c r="V7" t="n">
         <v>0.3115</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>X. CORTINA CAMPOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1874</v>
+        <v>2.7236</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7357</v>
+        <v>1.5809</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4517</v>
+        <v>1.1427</v>
       </c>
       <c r="G8" t="n">
-        <v>5.0381</v>
+        <v>1.2881</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1808</v>
+        <v>0.522</v>
       </c>
       <c r="I8" t="n">
-        <v>5.2188</v>
+        <v>0.7661</v>
       </c>
       <c r="J8" t="n">
-        <v>4.585</v>
+        <v>0.5677</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0249</v>
+        <v>0.4427</v>
       </c>
       <c r="L8" t="n">
-        <v>4.6099</v>
+        <v>0.125</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4531</v>
+        <v>0.7204</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1558</v>
+        <v>0.0793</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6089</v>
+        <v>0.641</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.4661</v>
+        <v>0.9163</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2828</v>
+        <v>0.9163</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7511</v>
+        <v>-0.1143</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4774</v>
+        <v>0.3797</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2738</v>
+        <v>-0.494</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6335</v>
+        <v>0.6335</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6231</v>
+        <v>0.6335</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.0104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6806</v>
+        <v>1.7621</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6157</v>
+        <v>-1.0387</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2963</v>
+        <v>2.8008</v>
       </c>
       <c r="G9" t="n">
         <v>1.5321</v>
@@ -1156,13 +1156,13 @@
         <v>1.2828</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6983</v>
+        <v>0.7798</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2941</v>
+        <v>0.2828</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.497</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.623</v>
+        <v>1.1007</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2482</v>
+        <v>-1.5227</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8712</v>
+        <v>2.6234</v>
       </c>
       <c r="G10" t="n">
         <v>0.9451000000000001</v>
@@ -1234,13 +1234,13 @@
         <v>2.0158</v>
       </c>
       <c r="S10" t="n">
-        <v>1.7225</v>
+        <v>1.2002</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7677</v>
+        <v>0.4932</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9547</v>
+        <v>0.707</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3115</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. FERRI BARCENAS</t>
+          <t>R. TORREGROSA ROCA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.506</v>
+        <v>0.5618</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3706</v>
+        <v>1.0207</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8766</v>
+        <v>-0.4589</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5652</v>
+        <v>2.3631</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5635</v>
+        <v>1.9848</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1287</v>
+        <v>0.3783</v>
       </c>
       <c r="J12" t="n">
-        <v>0.84</v>
+        <v>2.4792</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0959</v>
+        <v>2.8702</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7441</v>
+        <v>-0.391</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2748</v>
+        <v>-0.1161</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6594</v>
+        <v>-0.8854</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3846</v>
+        <v>0.7692</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1833</v>
+        <v>0.5498</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0995</v>
+        <v>2.3823</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3807</v>
+        <v>0.1829</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3288</v>
+        <v>0.3741</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0519</v>
+        <v>-0.1912</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6231</v>
+        <v>-2.5339</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. ROIG ARIÑO</t>
+          <t>P. FERRI BARCENAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3251</v>
+        <v>0.3633</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3251</v>
+        <v>-0.5629</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.9262</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3251</v>
+        <v>0.5652</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3251</v>
+        <v>-0.5635</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1.1287</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3251</v>
+        <v>0.84</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3251</v>
+        <v>0.0959</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.7441</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-0.2748</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>-0.6594</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>0.3846</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.1833</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>0.2379</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>0.1365</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>0.1014</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. TORREGROSA ROCA</t>
+          <t>T. ROIG ARIÑO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.08740000000000001</v>
+        <v>0.3251</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7183</v>
+        <v>0.3251</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8058</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3631</v>
+        <v>0.3251</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9848</v>
+        <v>0.3251</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3783</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4792</v>
+        <v>0.3251</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8702</v>
+        <v>0.3251</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.391</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1161</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8854</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7692</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3823</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4664</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0717</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.538</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.5339</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.5339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4163</v>
+        <v>-0.4079</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.6537</v>
+        <v>-1.6948</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2374</v>
+        <v>1.2869</v>
       </c>
       <c r="G15" t="n">
         <v>0.0115</v>
@@ -1624,13 +1624,13 @@
         <v>1.2828</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4727</v>
+        <v>0.4811</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2187</v>
+        <v>0.1776</v>
       </c>
       <c r="U15" t="n">
-        <v>0.254</v>
+        <v>0.3035</v>
       </c>
       <c r="V15" t="n">
         <v>-1.267</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>35.5436</v>
+        <v>36.09410000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>24.6343</v>
+        <v>25.185</v>
       </c>
       <c r="F16" t="n">
-        <v>10.9091</v>
+        <v>10.909</v>
       </c>
       <c r="G16" t="n">
         <v>36.2763</v>
@@ -1702,13 +1702,13 @@
         <v>18.3256</v>
       </c>
       <c r="S16" t="n">
-        <v>3.7594</v>
+        <v>4.309799999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2844</v>
+        <v>3.834899999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4747999999999999</v>
+        <v>0.4749</v>
       </c>
       <c r="V16" t="n">
         <v>-6.324400000000001</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.118</v>
+        <v>0.0277</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1213</v>
+        <v>-0.4097</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0032</v>
+        <v>0.4374</v>
       </c>
       <c r="G17" t="n">
         <v>-0.91</v>
@@ -1780,13 +1780,13 @@
         <v>1.8326</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4255</v>
+        <v>-0.2798</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0384</v>
+        <v>-0.3269</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.387</v>
+        <v>0.0471</v>
       </c>
       <c r="V17" t="n">
         <v>0.3011</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. HORTELANO ESCRIBA</t>
+          <t>F. BLASCO MANZANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.508</v>
+        <v>-0.5528</v>
       </c>
       <c r="E18" t="n">
-        <v>2.292</v>
+        <v>-0.7932</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.8</v>
+        <v>0.2404</v>
       </c>
       <c r="G18" t="n">
-        <v>-6.1964</v>
+        <v>-2.4336</v>
       </c>
       <c r="H18" t="n">
-        <v>-4.2727</v>
+        <v>-1.3434</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.9237</v>
+        <v>-1.0902</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.6045</v>
+        <v>-0.4184</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9635</v>
+        <v>-0.4184</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.641</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.5919</v>
+        <v>-2.0152</v>
       </c>
       <c r="N18" t="n">
-        <v>-3.3092</v>
+        <v>-0.925</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2827</v>
+        <v>-1.0902</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.8326</v>
+        <v>1.0995</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.5814</v>
+        <v>-0.9163</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7489</v>
+        <v>2.0158</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4976</v>
+        <v>-0.1742</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8107</v>
+        <v>-0.414</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3131</v>
+        <v>0.2398</v>
       </c>
       <c r="V18" t="n">
-        <v>6.0233</v>
+        <v>0.9554</v>
       </c>
       <c r="W18" t="n">
-        <v>6.6672</v>
+        <v>0.9554</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. BLASCO MANZANO</t>
+          <t>C. HORTELANO ESCRIBA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8034</v>
+        <v>-1.4521</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9855</v>
+        <v>1.042</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1822</v>
+        <v>-2.4941</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.4336</v>
+        <v>-6.1964</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3434</v>
+        <v>-4.2727</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0902</v>
+        <v>-1.9237</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4184</v>
+        <v>-1.6045</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4184</v>
+        <v>-0.9635</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.641</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0152</v>
+        <v>-4.5919</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.925</v>
+        <v>-3.3092</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0902</v>
+        <v>-1.2827</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0995</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9163</v>
+        <v>-4.5814</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0158</v>
+        <v>2.7489</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4247</v>
+        <v>0.5536</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6063</v>
+        <v>0.5607</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1816</v>
+        <v>-0.0072</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9554</v>
+        <v>6.0233</v>
       </c>
       <c r="W19" t="n">
-        <v>0.9554</v>
+        <v>6.6672</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. CARRION BALLESTER</t>
+          <t>R. MEDINA LERMA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3282</v>
+        <v>-2.2123</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0779</v>
+        <v>-1.2375</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2504</v>
+        <v>-0.9748</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.8011</v>
+        <v>-1.912</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5311</v>
+        <v>-0.4372</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.27</v>
+        <v>-1.4748</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3678</v>
+        <v>0.1826</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6499</v>
+        <v>0.1826</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2821</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-5.1689</v>
+        <v>-2.0946</v>
       </c>
       <c r="N20" t="n">
-        <v>-3.181</v>
+        <v>-0.6198</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.9879</v>
+        <v>-1.4748</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9163</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.6651</v>
+        <v>-1.8326</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7489</v>
+        <v>1.2828</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5333</v>
+        <v>-0.0413</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3635</v>
+        <v>0.0905</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1697</v>
+        <v>-0.1318</v>
       </c>
       <c r="V20" t="n">
-        <v>2.8559</v>
+        <v>0.2907</v>
       </c>
       <c r="W20" t="n">
-        <v>2.8559</v>
+        <v>0.3219</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.0312</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. MEDINA LERMA</t>
+          <t>R. CARRION BALLESTER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8286</v>
+        <v>-2.4405</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6221</v>
+        <v>-0.174</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2064</v>
+        <v>-2.2665</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.912</v>
+        <v>-4.8011</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4372</v>
+        <v>-1.5311</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4748</v>
+        <v>-3.27</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1826</v>
+        <v>0.3678</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1826</v>
+        <v>1.6499</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-1.2821</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0946</v>
+        <v>-5.1689</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6198</v>
+        <v>-3.181</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4748</v>
+        <v>-1.9879</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5498</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.8326</v>
+        <v>-3.6651</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2828</v>
+        <v>2.7489</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6575</v>
+        <v>0.421</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2941</v>
+        <v>0.2674</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3634</v>
+        <v>0.1536</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2907</v>
+        <v>2.8559</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3219</v>
+        <v>2.8559</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.0312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7711</v>
+        <v>-3.519</v>
       </c>
       <c r="E22" t="n">
         <v>-1.8087</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9624</v>
+        <v>-1.7103</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8898</v>
@@ -2170,13 +2170,13 @@
         <v>0.9163</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6142</v>
+        <v>-0.3622</v>
       </c>
       <c r="T22" t="n">
         <v>-0.3673</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.247</v>
+        <v>0.0051</v>
       </c>
       <c r="V22" t="n">
         <v>-1.267</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2227</v>
+        <v>-3.6078</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0146</v>
+        <v>-0.7262</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.208</v>
+        <v>-2.8816</v>
       </c>
       <c r="G23" t="n">
         <v>-5.32</v>
@@ -2248,13 +2248,13 @@
         <v>1.6493</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2246</v>
+        <v>-0.6097</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3318</v>
+        <v>-0.0433</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8928</v>
+        <v>-0.5664</v>
       </c>
       <c r="V23" t="n">
         <v>1.5889</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.0929</v>
+        <v>-4.8758</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2032</v>
+        <v>-1.0109</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.8897</v>
+        <v>-3.8649</v>
       </c>
       <c r="G24" t="n">
         <v>-1.1275</v>
@@ -2326,13 +2326,13 @@
         <v>0.1833</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6984</v>
+        <v>-0.4813</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3303</v>
+        <v>-0.138</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3681</v>
+        <v>-0.3433</v>
       </c>
       <c r="V24" t="n">
         <v>-2.5339</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.7143</v>
+        <v>-6.5118</v>
       </c>
       <c r="E25" t="n">
         <v>-3.3061</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.4082</v>
+        <v>-3.2057</v>
       </c>
       <c r="G25" t="n">
         <v>-7.2684</v>
@@ -2404,13 +2404,13 @@
         <v>1.4661</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6292</v>
+        <v>-0.4267</v>
       </c>
       <c r="T25" t="n">
         <v>-0.0565</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5726</v>
+        <v>-0.3701</v>
       </c>
       <c r="V25" t="n">
         <v>0.6335</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-9.1564</v>
+        <v>-8.379899999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.0617</v>
+        <v>-2.3886</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.0947</v>
+        <v>-5.9913</v>
       </c>
       <c r="G26" t="n">
         <v>-4.4173</v>
@@ -2482,13 +2482,13 @@
         <v>1.6493</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.1161</v>
+        <v>-0.3395</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6244</v>
+        <v>0.0487</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4916</v>
+        <v>-0.3882</v>
       </c>
       <c r="V26" t="n">
         <v>-2.5235</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-35.5436</v>
+        <v>-33.5243</v>
       </c>
       <c r="E27" t="n">
-        <v>-10.9091</v>
+        <v>-10.8129</v>
       </c>
       <c r="F27" t="n">
-        <v>-24.6344</v>
+        <v>-22.7114</v>
       </c>
       <c r="G27" t="n">
         <v>-36.2761</v>
@@ -2539,7 +2539,7 @@
         <v>2.3974</v>
       </c>
       <c r="L27" t="n">
-        <v>-8.172700000000001</v>
+        <v>-8.172699999999999</v>
       </c>
       <c r="M27" t="n">
         <v>-30.5008</v>
@@ -2560,13 +2560,13 @@
         <v>16.4933</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.759300000000001</v>
+        <v>-1.7401</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.4748999999999998</v>
+        <v>-0.3787</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.2843</v>
+        <v>-1.3614</v>
       </c>
       <c r="V27" t="n">
         <v>6.324399999999999</v>
